--- a/reports/weekly_report_20260612.xlsx
+++ b/reports/weekly_report_20260612.xlsx
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2749</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="9">
@@ -515,7 +515,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>87.32%</t>
+          <t>87.38%</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4.0600%</t>
+          <t>3.4100%</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-19 07:46:28</t>
+          <t>2026-06-19 08:08:35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -718,11 +718,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4772</v>
+        <v>5094</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-19 07:46:28</t>
+          <t>2026-06-19 08:08:35</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
